--- a/public/exports-with-coowners/29189765.xlsx
+++ b/public/exports-with-coowners/29189765.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/29189765.xlsx
+++ b/public/exports-with-coowners/29189765.xlsx
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvejen 385A</t>
+          <t xml:space="preserve">Tinghusgade 15A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,30 +4851,30 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1493949</t>
+          <t xml:space="preserve">5142582</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J65">
-        <v>1140</v>
+        <v>2235</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679342</t>
+          <t xml:space="preserve">311680381</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-12</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15A</t>
+          <t xml:space="preserve">Tinghusgade 15C</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J66">
-        <v>2235</v>
+        <v>1811</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15C</t>
+          <t xml:space="preserve">Tinghusgade 15F</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>1811</v>
+        <v>3334</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 15F</t>
+          <t xml:space="preserve">Fynsgade 39</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142582</t>
+          <t xml:space="preserve">315128, 315129, 315130</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="J68">
-        <v>3334</v>
+        <v>3456</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680381</t>
+          <t xml:space="preserve">311684239</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-12</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fynsgade 39</t>
+          <t xml:space="preserve">Sydtoften 100A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">315128, 315129, 315130</t>
+          <t xml:space="preserve">315575, 315578</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J69">
-        <v>3456</v>
+        <v>653</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684239</t>
+          <t xml:space="preserve">311684378</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 100A</t>
+          <t xml:space="preserve">Sydtoften 102</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315578</t>
+          <t xml:space="preserve">315575, 315576</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>653</v>
+        <v>2655</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684378</t>
+          <t xml:space="preserve">311684376</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 102</t>
+          <t xml:space="preserve">Buen 6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">315575, 315576</t>
+          <t xml:space="preserve">9084190</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="J71">
-        <v>2655</v>
+        <v>607</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684376</t>
+          <t xml:space="preserve">311686103</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CB Group af 2017 ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2033-06-07</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>607</v>
+        <v>1457</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buen 6</t>
+          <t xml:space="preserve">Degnelodden 3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6623</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084190</t>
+          <t xml:space="preserve">315952, 315953, 315954</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>1457</v>
+        <v>2824</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686103</t>
+          <t xml:space="preserve">311686146</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Degnelodden 3</t>
+          <t xml:space="preserve">Drivvejen 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">315952, 315953, 315954</t>
+          <t xml:space="preserve">5146067</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,11 +5535,11 @@
         </is>
       </c>
       <c r="J74">
-        <v>2824</v>
+        <v>6667</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686146</t>
+          <t xml:space="preserve">311686166</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drivvejen 1</t>
+          <t xml:space="preserve">Kirkevej 8A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6623</t>
+          <t xml:space="preserve">7250</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5146067</t>
+          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>6667</v>
+        <v>1775</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686166</t>
+          <t xml:space="preserve">311686186</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8A</t>
+          <t xml:space="preserve">Kirkevej 8B</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">315561, 315562, 315563, 315564</t>
+          <t xml:space="preserve">315563</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J76">
-        <v>1775</v>
+        <v>264</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686186</t>
+          <t xml:space="preserve">311686187</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8B</t>
+          <t xml:space="preserve">Rahbæksvej 18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">315563</t>
+          <t xml:space="preserve">321325, 321326, 321327</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>264</v>
+        <v>3813</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686187</t>
+          <t xml:space="preserve">311686196</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbæksvej 18</t>
+          <t xml:space="preserve">Teglgaardsvej 7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">321325, 321326, 321327</t>
+          <t xml:space="preserve">735144, 5077351</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J78">
-        <v>3813</v>
+        <v>1538</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686196</t>
+          <t xml:space="preserve">311686096</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgaardsvej 7</t>
+          <t xml:space="preserve">Tinghusgade 12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">735144, 5077351</t>
+          <t xml:space="preserve">5142495</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
-        <v>1538</v>
+        <v>2526</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686096</t>
+          <t xml:space="preserve">311686205</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 12</t>
+          <t xml:space="preserve">Tinghusgade 16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,15 +5981,15 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>2526</v>
+        <v>1991</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686205</t>
+          <t xml:space="preserve">311686199</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">Hedens Boligselskab</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinghusgade 16</t>
+          <t xml:space="preserve">Sydtoften 381B</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5142495</t>
+          <t xml:space="preserve">315579, 315580</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,21 +6060,21 @@
         </is>
       </c>
       <c r="J81">
-        <v>1991</v>
+        <v>1757</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686199</t>
+          <t xml:space="preserve">311711256</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-07</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydtoften 381B</t>
+          <t xml:space="preserve">Nygade 29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">315579, 315580</t>
+          <t xml:space="preserve">315080, 315082</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>1757</v>
+        <v>3573</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711256</t>
+          <t xml:space="preserve">311711550</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2033-09-29</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedens Boligselskab</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 29</t>
+          <t xml:space="preserve">Vesterbrogade 1A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">315080, 315082</t>
+          <t xml:space="preserve">9658844</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,21 +6210,21 @@
         </is>
       </c>
       <c r="J83">
-        <v>3573</v>
+        <v>519</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711550</t>
+          <t xml:space="preserve">311735594</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-29</t>
+          <t xml:space="preserve">2034-01-28</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,40 +6266,40 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbrogade 1A</t>
+          <t xml:space="preserve">Skovvej 15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">7260</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9658844</t>
+          <t xml:space="preserve">9084136</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J84">
-        <v>519</v>
+        <v>1099</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735594</t>
+          <t xml:space="preserve">311771547</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">STD Klima og Byggeri</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-28</t>
+          <t xml:space="preserve">2034-07-04</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billund Kommune</t>
+          <t xml:space="preserve">KIRKBI Property A/S</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6341,40 +6341,40 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 15</t>
+          <t xml:space="preserve">Byens Plads 3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260</t>
+          <t xml:space="preserve">7190</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9084136</t>
+          <t xml:space="preserve">321351, 321352, 321353</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>1099</v>
+        <v>1478</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771547</t>
+          <t xml:space="preserve">311846016</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD Klima og Byggeri</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-04</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIRKBI Property A/S</t>
+          <t xml:space="preserve">Billund Kommune</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byens Plads 3</t>
+          <t xml:space="preserve">Tingvejen 385A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">321351, 321352, 321353</t>
+          <t xml:space="preserve">1493949</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="J86">
-        <v>1478</v>
+        <v>1140</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846016</t>
+          <t xml:space="preserve">311928758</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">

--- a/public/exports-with-coowners/29189765.xlsx
+++ b/public/exports-with-coowners/29189765.xlsx
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928758</t>
+          <t xml:space="preserve">311928752</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
